--- a/analysis_sample3.xlsx
+++ b/analysis_sample3.xlsx
@@ -2692,7 +2692,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2704,8 +2704,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2715,6 +2718,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -2740,11 +2748,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3172,7 +3182,7 @@
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H2" t="s">
@@ -3181,7 +3191,7 @@
       <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K2">
@@ -3213,7 +3223,7 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -3228,7 +3238,7 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H3" t="s">
@@ -3237,13 +3247,13 @@
       <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M3" t="s">
@@ -3261,7 +3271,7 @@
       <c r="Q3">
         <v>120</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="3">
         <v>0.77</v>
       </c>
     </row>
@@ -3269,7 +3279,7 @@
       <c r="A4" t="s">
         <v>37</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>5</v>
       </c>
       <c r="C4" t="s">
@@ -3299,7 +3309,7 @@
       <c r="K4">
         <v>0.46</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="M4" t="s">
@@ -3325,7 +3335,7 @@
       <c r="A5" t="s">
         <v>46</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -3461,7 +3471,7 @@
       <c r="I7" t="s">
         <v>70</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="K7">
@@ -3549,7 +3559,7 @@
       <c r="A9" t="s">
         <v>82</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" t="s">
@@ -3661,7 +3671,7 @@
       <c r="A11" t="s">
         <v>100</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>6</v>
       </c>
       <c r="C11" t="s">
@@ -3762,7 +3772,7 @@
       <c r="P12">
         <v>3</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="2">
         <v>186</v>
       </c>
       <c r="R12">
@@ -3773,7 +3783,7 @@
       <c r="A13" t="s">
         <v>117</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>4</v>
       </c>
       <c r="C13" t="s">
@@ -3829,7 +3839,7 @@
       <c r="A14" t="s">
         <v>126</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" t="s">
@@ -3844,7 +3854,7 @@
       <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H14" t="s">
@@ -3853,7 +3863,7 @@
       <c r="I14" t="s">
         <v>129</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="K14">
@@ -3874,10 +3884,10 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="2">
         <v>143</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="3">
         <v>0.67</v>
       </c>
     </row>
@@ -3885,7 +3895,7 @@
       <c r="A15" t="s">
         <v>131</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" t="s">
@@ -3915,7 +3925,7 @@
       <c r="K15">
         <v>0.99</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>137</v>
       </c>
       <c r="M15" t="s">
@@ -3930,10 +3940,10 @@
       <c r="P15">
         <v>2</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>308</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="3">
         <v>0.51</v>
       </c>
     </row>
@@ -4024,10 +4034,10 @@
       <c r="J17" t="s">
         <v>152</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>0.82</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="2" t="s">
         <v>153</v>
       </c>
       <c r="M17" t="s">
@@ -4042,7 +4052,7 @@
       <c r="P17">
         <v>4</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="2">
         <v>1275</v>
       </c>
       <c r="R17">
@@ -4053,7 +4063,7 @@
       <c r="A18" t="s">
         <v>155</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>6</v>
       </c>
       <c r="C18" t="s">
@@ -4083,7 +4093,7 @@
       <c r="K18">
         <v>0.43</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="2" t="s">
         <v>160</v>
       </c>
       <c r="M18" t="s">
@@ -4098,10 +4108,10 @@
       <c r="P18">
         <v>6</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="2">
         <v>151</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="3">
         <v>0.51</v>
       </c>
     </row>
@@ -4154,7 +4164,7 @@
       <c r="P19">
         <v>2.3</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="2">
         <v>218</v>
       </c>
       <c r="R19">
@@ -4165,7 +4175,7 @@
       <c r="A20" t="s">
         <v>171</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>4</v>
       </c>
       <c r="C20" t="s">
@@ -4221,7 +4231,7 @@
       <c r="A21" t="s">
         <v>179</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>2</v>
       </c>
       <c r="C21" t="s">
@@ -4251,7 +4261,7 @@
       <c r="K21">
         <v>0.79</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" s="2" t="s">
         <v>185</v>
       </c>
       <c r="M21" t="s">
@@ -4277,7 +4287,7 @@
       <c r="A22" t="s">
         <v>187</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>4</v>
       </c>
       <c r="C22" t="s">
@@ -4333,7 +4343,7 @@
       <c r="A23" t="s">
         <v>194</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>6</v>
       </c>
       <c r="C23" t="s">
@@ -4357,10 +4367,10 @@
       <c r="I23" t="s">
         <v>198</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>0.55</v>
       </c>
       <c r="L23" t="s">
@@ -4389,7 +4399,7 @@
       <c r="A24" t="s">
         <v>202</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" t="s">
@@ -4419,7 +4429,7 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="2" t="s">
         <v>207</v>
       </c>
       <c r="M24" t="s">
@@ -4434,10 +4444,10 @@
       <c r="P24">
         <v>1</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="2">
         <v>294</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="3">
         <v>0.51</v>
       </c>
     </row>
@@ -4445,7 +4455,7 @@
       <c r="A25" t="s">
         <v>208</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>5</v>
       </c>
       <c r="C25" t="s">
@@ -4516,7 +4526,7 @@
       <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="2" t="s">
         <v>218</v>
       </c>
       <c r="H26" t="s">
@@ -4525,7 +4535,7 @@
       <c r="I26" t="s">
         <v>22</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="2" t="s">
         <v>220</v>
       </c>
       <c r="K26">
@@ -4557,7 +4567,7 @@
       <c r="A27" t="s">
         <v>223</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>5</v>
       </c>
       <c r="C27" t="s">
@@ -4572,7 +4582,7 @@
       <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="2" t="s">
         <v>224</v>
       </c>
       <c r="H27" t="s">
@@ -4581,7 +4591,7 @@
       <c r="I27" t="s">
         <v>22</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="2" t="s">
         <v>226</v>
       </c>
       <c r="K27">
@@ -4605,7 +4615,7 @@
       <c r="Q27">
         <v>66</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="3">
         <v>0.53</v>
       </c>
     </row>
@@ -4613,7 +4623,7 @@
       <c r="A28" t="s">
         <v>229</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>6</v>
       </c>
       <c r="C28" t="s">
@@ -4628,7 +4638,7 @@
       <c r="F28" t="s">
         <v>22</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="2" t="s">
         <v>230</v>
       </c>
       <c r="H28" t="s">
@@ -4637,10 +4647,10 @@
       <c r="I28" t="s">
         <v>232</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>0.47</v>
       </c>
       <c r="L28" t="s">
@@ -4661,7 +4671,7 @@
       <c r="Q28">
         <v>75</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="3">
         <v>0.61</v>
       </c>
     </row>
@@ -4669,7 +4679,7 @@
       <c r="A29" t="s">
         <v>236</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>5</v>
       </c>
       <c r="C29" t="s">
@@ -4684,7 +4694,7 @@
       <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>237</v>
       </c>
       <c r="H29" t="s">
@@ -4693,7 +4703,7 @@
       <c r="I29" t="s">
         <v>239</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="2" t="s">
         <v>240</v>
       </c>
       <c r="K29">
@@ -4717,7 +4727,7 @@
       <c r="Q29">
         <v>22</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="3">
         <v>0.53</v>
       </c>
     </row>
@@ -4725,7 +4735,7 @@
       <c r="A30" t="s">
         <v>243</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>3</v>
       </c>
       <c r="C30" t="s">
@@ -4755,7 +4765,7 @@
       <c r="K30">
         <v>0.5</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" s="2" t="s">
         <v>250</v>
       </c>
       <c r="M30" t="s">
@@ -4837,7 +4847,7 @@
       <c r="A32" t="s">
         <v>262</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>1</v>
       </c>
       <c r="C32" t="s">
@@ -4852,7 +4862,7 @@
       <c r="F32" t="s">
         <v>22</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="2" t="s">
         <v>263</v>
       </c>
       <c r="H32" t="s">
@@ -4861,13 +4871,13 @@
       <c r="I32" t="s">
         <v>22</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="2" t="s">
         <v>265</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" s="2" t="s">
         <v>266</v>
       </c>
       <c r="M32" t="s">
@@ -4885,7 +4895,7 @@
       <c r="Q32">
         <v>114</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="3">
         <v>0.77</v>
       </c>
     </row>
@@ -4949,7 +4959,7 @@
       <c r="A34" t="s">
         <v>276</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>5</v>
       </c>
       <c r="C34" t="s">
@@ -4994,7 +5004,7 @@
       <c r="P34">
         <v>5</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="2">
         <v>139</v>
       </c>
       <c r="R34">
@@ -5005,7 +5015,7 @@
       <c r="A35" t="s">
         <v>283</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <v>6</v>
       </c>
       <c r="C35" t="s">
@@ -5032,7 +5042,7 @@
       <c r="J35" t="s">
         <v>287</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="2">
         <v>0.61</v>
       </c>
       <c r="L35" t="s">
@@ -5061,7 +5071,7 @@
       <c r="A36" t="s">
         <v>290</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>6</v>
       </c>
       <c r="C36" t="s">
@@ -5091,7 +5101,7 @@
       <c r="K36">
         <v>0.46</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="2" t="s">
         <v>295</v>
       </c>
       <c r="M36" t="s">
@@ -5117,7 +5127,7 @@
       <c r="A37" t="s">
         <v>297</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>6</v>
       </c>
       <c r="C37" t="s">
@@ -5132,7 +5142,7 @@
       <c r="F37" t="s">
         <v>22</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H37" t="s">
@@ -5141,13 +5151,13 @@
       <c r="I37" t="s">
         <v>300</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="2" t="s">
         <v>301</v>
       </c>
       <c r="K37">
         <v>0.46</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" s="2" t="s">
         <v>302</v>
       </c>
       <c r="M37" t="s">
@@ -5165,7 +5175,7 @@
       <c r="Q37">
         <v>49</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="3">
         <v>0.71</v>
       </c>
     </row>
@@ -5189,26 +5199,26 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7374,65 +7384,65 @@
     <col min="17" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>308</v>
       </c>
     </row>

--- a/analysis_sample3.xlsx
+++ b/analysis_sample3.xlsx
@@ -63,7 +63,7 @@
     <t>Avg Commits</t>
   </si>
   <si>
-    <t>Avg Changes/h</t>
+    <t>Avg Changes/h over session</t>
   </si>
   <si>
     <t>Index</t>
